--- a/Assets/Excel/excel.xlsx
+++ b/Assets/Excel/excel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="2"/>
+    <workbookView windowHeight="17775" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
@@ -2869,7 +2869,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G2">
         <v>30</v>

--- a/Assets/Excel/excel.xlsx
+++ b/Assets/Excel/excel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775" activeTab="2"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="106">
   <si>
     <t>道具ID</t>
   </si>
@@ -242,9 +242,6 @@
     <t>掉落速度软上限，单位 m/s。超过后会施加向上阻力。</t>
   </si>
   <si>
-    <t>水面张力系数。控制穿过水面时的竖向水面力。</t>
-  </si>
-  <si>
     <t>受力系数。控制绳子拉船/反拉相关的全局力倍率。</t>
   </si>
   <si>
@@ -278,6 +275,9 @@
     <t>物品质量系数。物品重量转换为 Unity Rigidbody2D.mass 的全局倍率。</t>
   </si>
   <si>
+    <t>入水初速度</t>
+  </si>
+  <si>
     <t>关卡ID</t>
   </si>
   <si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>拼凑时间（秒）</t>
+  </si>
+  <si>
+    <t>水面张力</t>
   </si>
   <si>
     <t>低级</t>
@@ -2706,7 +2709,7 @@
         <v>70</v>
       </c>
       <c r="B4">
-        <v>0.02</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2714,7 +2717,7 @@
         <v>71</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2722,7 +2725,7 @@
         <v>72</v>
       </c>
       <c r="B6">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2730,7 +2733,7 @@
         <v>73</v>
       </c>
       <c r="B7">
-        <v>0.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2738,7 +2741,7 @@
         <v>74</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2746,7 +2749,7 @@
         <v>75</v>
       </c>
       <c r="B9">
-        <v>0.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2754,7 +2757,7 @@
         <v>76</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2762,7 +2765,7 @@
         <v>77</v>
       </c>
       <c r="B11">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2770,7 +2773,7 @@
         <v>78</v>
       </c>
       <c r="B12">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2778,10 +2781,10 @@
         <v>79</v>
       </c>
       <c r="B13">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="27" spans="1:2">
       <c r="A14" s="3" t="s">
         <v>80</v>
       </c>
@@ -2789,12 +2792,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" ht="27" spans="1:2">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:2">
+      <c r="A15" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B15">
-        <v>1</v>
+      <c r="B15" s="1">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2807,13 +2810,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="12" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>82</v>
       </c>
@@ -2850,8 +2853,11 @@
       <c r="L1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2869,7 +2875,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G2">
         <v>30</v>
@@ -2884,13 +2890,16 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L2">
         <v>180</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2923,13 +2932,16 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L3">
         <v>180</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2962,13 +2974,16 @@
         <v>1.05392156862745</v>
       </c>
       <c r="K4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L4">
         <v>180</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3001,13 +3016,16 @@
         <v>1.31944444444444</v>
       </c>
       <c r="K5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5">
         <v>180</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3040,13 +3058,16 @@
         <v>1.55701754385965</v>
       </c>
       <c r="K6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L6">
         <v>180</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3079,13 +3100,16 @@
         <v>1.75</v>
       </c>
       <c r="K7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L7">
         <v>180</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3118,13 +3142,16 @@
         <v>1.9047619047619</v>
       </c>
       <c r="K8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L8">
         <v>180</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3157,13 +3184,16 @@
         <v>2.04545454545455</v>
       </c>
       <c r="K9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L9">
         <v>180</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="M9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3196,13 +3226,16 @@
         <v>2.17391304347826</v>
       </c>
       <c r="K10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L10">
         <v>180</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="M10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3235,10 +3268,13 @@
         <v>2.29166666666667</v>
       </c>
       <c r="K11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L11">
         <v>180</v>
+      </c>
+      <c r="M11">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3259,7 +3295,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1">
         <v>20</v>
@@ -3267,7 +3303,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3275,7 +3311,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3283,7 +3319,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -3291,7 +3327,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3299,7 +3335,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/Assets/Excel/excel.xlsx
+++ b/Assets/Excel/excel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="111">
   <si>
     <t>道具ID</t>
   </si>
@@ -125,6 +125,9 @@
     <t>船锚玩具</t>
   </si>
   <si>
+    <t>chuanmao</t>
+  </si>
+  <si>
     <t>一罐鱼饵</t>
   </si>
   <si>
@@ -143,15 +146,27 @@
     <t>文字</t>
   </si>
   <si>
+    <t>cigaC</t>
+  </si>
+  <si>
     <t>字母I</t>
   </si>
   <si>
+    <t>cigaI</t>
+  </si>
+  <si>
     <t>字母G</t>
   </si>
   <si>
+    <t>cigaG</t>
+  </si>
+  <si>
     <t>字母A</t>
   </si>
   <si>
+    <t>cigaA</t>
+  </si>
+  <si>
     <t>手机</t>
   </si>
   <si>
@@ -191,13 +206,13 @@
     <t>啤酒瓶</t>
   </si>
   <si>
-    <t>猫</t>
-  </si>
-  <si>
-    <t>狗</t>
-  </si>
-  <si>
-    <t>马</t>
+    <t>小布</t>
+  </si>
+  <si>
+    <t>小美</t>
+  </si>
+  <si>
+    <t>曼波</t>
   </si>
   <si>
     <t>“区”</t>
@@ -520,12 +535,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -846,7 +867,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -870,16 +891,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
@@ -888,89 +909,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -980,6 +1001,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1337,7 +1361,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
@@ -1407,7 +1431,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C4" t="s">
@@ -1477,7 +1501,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
@@ -1512,7 +1536,7 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
@@ -1547,7 +1571,7 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
@@ -1582,7 +1606,7 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
@@ -1624,7 +1648,7 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E10">
         <v>0.2</v>
@@ -1652,8 +1676,8 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>31</v>
+      <c r="B11" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
@@ -1687,8 +1711,8 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>32</v>
+      <c r="B12" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>
@@ -1722,11 +1746,11 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>33</v>
+      <c r="B13" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
@@ -1758,13 +1782,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E14">
         <v>0.73</v>
@@ -1793,13 +1817,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
         <v>37</v>
       </c>
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E15">
         <v>0.73</v>
@@ -1828,13 +1852,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="E16">
         <v>0.73</v>
@@ -1863,13 +1887,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E17">
         <v>0.73</v>
@@ -1898,13 +1922,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E18">
         <v>0.42</v>
@@ -1932,11 +1956,11 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>41</v>
+      <c r="B19" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
@@ -1967,8 +1991,8 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>43</v>
+      <c r="B20" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
@@ -2002,8 +2026,8 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>44</v>
+      <c r="B21" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
@@ -2037,11 +2061,11 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>45</v>
+      <c r="B22" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
         <v>19</v>
@@ -2072,8 +2096,8 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>47</v>
+      <c r="B23" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -2107,11 +2131,11 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>48</v>
+      <c r="B24" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
@@ -2142,8 +2166,8 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>50</v>
+      <c r="B25" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
@@ -2177,11 +2201,11 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>51</v>
+      <c r="B26" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D26" t="s">
         <v>13</v>
@@ -2212,11 +2236,11 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>52</v>
+      <c r="B27" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D27" t="s">
         <v>16</v>
@@ -2248,13 +2272,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E28">
         <v>4.6</v>
@@ -2283,13 +2307,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E29">
         <v>2.64</v>
@@ -2317,11 +2341,11 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>55</v>
+      <c r="B30" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D30" t="s">
         <v>24</v>
@@ -2352,11 +2376,11 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>56</v>
+      <c r="B31" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
@@ -2387,11 +2411,11 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>57</v>
+      <c r="B32" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>
@@ -2422,11 +2446,11 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>58</v>
+      <c r="B33" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
         <v>16</v>
@@ -2457,11 +2481,11 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>59</v>
+      <c r="B34" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
@@ -2492,11 +2516,11 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>61</v>
+      <c r="B35" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="C35" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D35" t="s">
         <v>22</v>
@@ -2527,8 +2551,8 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>62</v>
+      <c r="B36" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
@@ -2562,11 +2586,11 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>63</v>
+      <c r="B37" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D37" t="s">
         <v>26</v>
@@ -2597,11 +2621,11 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>64</v>
+      <c r="B38" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>
@@ -2633,7 +2657,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
@@ -2682,15 +2706,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B2">
         <v>15</v>
@@ -2698,7 +2722,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -2706,7 +2730,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2714,7 +2738,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B5">
         <v>0.18</v>
@@ -2722,7 +2746,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B6">
         <v>0.1</v>
@@ -2730,7 +2754,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -2738,7 +2762,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B8">
         <v>0.3</v>
@@ -2746,7 +2770,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -2754,7 +2778,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B10">
         <v>0.8</v>
@@ -2762,7 +2786,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -2770,7 +2794,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B12">
         <v>0.02</v>
@@ -2778,7 +2802,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2786,7 +2810,7 @@
     </row>
     <row r="14" ht="27" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -2794,7 +2818,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B15" s="1">
         <v>10</v>
@@ -2818,43 +2842,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="M1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2890,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="L2">
         <v>180</v>
@@ -2932,7 +2956,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L3">
         <v>180</v>
@@ -2974,7 +2998,7 @@
         <v>1.05392156862745</v>
       </c>
       <c r="K4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="L4">
         <v>180</v>
@@ -3016,7 +3040,7 @@
         <v>1.31944444444444</v>
       </c>
       <c r="K5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L5">
         <v>180</v>
@@ -3058,7 +3082,7 @@
         <v>1.55701754385965</v>
       </c>
       <c r="K6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="L6">
         <v>180</v>
@@ -3100,7 +3124,7 @@
         <v>1.75</v>
       </c>
       <c r="K7" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="L7">
         <v>180</v>
@@ -3142,7 +3166,7 @@
         <v>1.9047619047619</v>
       </c>
       <c r="K8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="L8">
         <v>180</v>
@@ -3184,7 +3208,7 @@
         <v>2.04545454545455</v>
       </c>
       <c r="K9" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="L9">
         <v>180</v>
@@ -3226,7 +3250,7 @@
         <v>2.17391304347826</v>
       </c>
       <c r="K10" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="L10">
         <v>180</v>
@@ -3268,7 +3292,7 @@
         <v>2.29166666666667</v>
       </c>
       <c r="K11" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="L11">
         <v>180</v>
@@ -3295,7 +3319,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B1">
         <v>20</v>
@@ -3303,7 +3327,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3311,7 +3335,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3319,7 +3343,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -3327,7 +3351,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3335,7 +3359,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/Assets/Excel/excel.xlsx
+++ b/Assets/Excel/excel.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="114">
   <si>
     <t>道具ID</t>
   </si>
@@ -215,6 +215,9 @@
     <t>曼波</t>
   </si>
   <si>
+    <t>manbo</t>
+  </si>
+  <si>
     <t>“区”</t>
   </si>
   <si>
@@ -242,7 +245,13 @@
     <t>奶龙</t>
   </si>
   <si>
+    <t>nailong</t>
+  </si>
+  <si>
     <t>我的刀盾</t>
+  </si>
+  <si>
+    <t>daodun</t>
   </si>
   <si>
     <t>中文参数解释</t>
@@ -991,7 +1000,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1003,6 +1012,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2341,14 +2353,14 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E30">
         <v>4.6</v>
@@ -2377,7 +2389,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
         <v>37</v>
@@ -2412,7 +2424,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
         <v>51</v>
@@ -2447,7 +2459,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C33" t="s">
         <v>35</v>
@@ -2482,10 +2494,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
@@ -2517,7 +2529,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C35" t="s">
         <v>47</v>
@@ -2552,7 +2564,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
@@ -2587,7 +2599,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C37" t="s">
         <v>35</v>
@@ -2621,14 +2633,14 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>69</v>
+      <c r="B38" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="C38" t="s">
         <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="E38">
         <v>0.73</v>
@@ -2657,13 +2669,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="E39">
         <v>1.75</v>
@@ -2706,15 +2718,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>15</v>
@@ -2722,7 +2734,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -2730,7 +2742,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2738,7 +2750,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B5">
         <v>0.18</v>
@@ -2746,7 +2758,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B6">
         <v>0.1</v>
@@ -2754,7 +2766,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -2762,7 +2774,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B8">
         <v>0.3</v>
@@ -2770,7 +2782,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -2778,7 +2790,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B10">
         <v>0.8</v>
@@ -2786,7 +2798,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -2794,7 +2806,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B12">
         <v>0.02</v>
@@ -2802,7 +2814,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2810,7 +2822,7 @@
     </row>
     <row r="14" ht="27" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -2818,7 +2830,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B15" s="1">
         <v>10</v>
@@ -2842,43 +2854,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2914,7 +2926,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L2">
         <v>180</v>
@@ -2956,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L3">
         <v>180</v>
@@ -2998,7 +3010,7 @@
         <v>1.05392156862745</v>
       </c>
       <c r="K4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L4">
         <v>180</v>
@@ -3040,7 +3052,7 @@
         <v>1.31944444444444</v>
       </c>
       <c r="K5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L5">
         <v>180</v>
@@ -3082,7 +3094,7 @@
         <v>1.55701754385965</v>
       </c>
       <c r="K6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L6">
         <v>180</v>
@@ -3124,7 +3136,7 @@
         <v>1.75</v>
       </c>
       <c r="K7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L7">
         <v>180</v>
@@ -3166,7 +3178,7 @@
         <v>1.9047619047619</v>
       </c>
       <c r="K8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L8">
         <v>180</v>
@@ -3208,7 +3220,7 @@
         <v>2.04545454545455</v>
       </c>
       <c r="K9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L9">
         <v>180</v>
@@ -3250,7 +3262,7 @@
         <v>2.17391304347826</v>
       </c>
       <c r="K10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L10">
         <v>180</v>
@@ -3292,7 +3304,7 @@
         <v>2.29166666666667</v>
       </c>
       <c r="K11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L11">
         <v>180</v>
@@ -3319,7 +3331,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B1">
         <v>20</v>
@@ -3327,7 +3339,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3335,7 +3347,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3343,7 +3355,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -3351,7 +3363,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3359,7 +3371,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/Assets/Excel/excel.xlsx
+++ b/Assets/Excel/excel.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="116">
   <si>
     <t>道具ID</t>
   </si>
@@ -227,6 +227,9 @@
     <t>西瓜</t>
   </si>
   <si>
+    <t>xigua</t>
+  </si>
+  <si>
     <t>黄油</t>
   </si>
   <si>
@@ -240,6 +243,9 @@
   </si>
   <si>
     <t>青蛙教练</t>
+  </si>
+  <si>
+    <t>frog</t>
   </si>
   <si>
     <t>奶龙</t>
@@ -1000,7 +1006,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1012,6 +1018,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2458,14 +2467,14 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="6" t="s">
         <v>64</v>
       </c>
       <c r="C33" t="s">
         <v>35</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="E33">
         <v>1.52</v>
@@ -2494,10 +2503,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
@@ -2529,7 +2538,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
         <v>47</v>
@@ -2564,7 +2573,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
@@ -2598,14 +2607,14 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>69</v>
+      <c r="B37" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="C37" t="s">
         <v>35</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="E37">
         <v>1.01</v>
@@ -2634,13 +2643,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C38" t="s">
         <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E38">
         <v>0.73</v>
@@ -2669,13 +2678,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E39">
         <v>1.75</v>
@@ -2718,15 +2727,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B2">
         <v>15</v>
@@ -2734,7 +2743,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -2742,7 +2751,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2750,7 +2759,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B5">
         <v>0.18</v>
@@ -2758,7 +2767,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B6">
         <v>0.1</v>
@@ -2766,7 +2775,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -2774,7 +2783,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8">
         <v>0.3</v>
@@ -2782,7 +2791,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -2790,7 +2799,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B10">
         <v>0.8</v>
@@ -2798,7 +2807,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -2806,7 +2815,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12">
         <v>0.02</v>
@@ -2814,7 +2823,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2822,7 +2831,7 @@
     </row>
     <row r="14" ht="27" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -2830,7 +2839,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B15" s="1">
         <v>10</v>
@@ -2854,43 +2863,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2926,7 +2935,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L2">
         <v>180</v>
@@ -2968,7 +2977,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L3">
         <v>180</v>
@@ -3010,7 +3019,7 @@
         <v>1.05392156862745</v>
       </c>
       <c r="K4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L4">
         <v>180</v>
@@ -3052,7 +3061,7 @@
         <v>1.31944444444444</v>
       </c>
       <c r="K5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L5">
         <v>180</v>
@@ -3094,7 +3103,7 @@
         <v>1.55701754385965</v>
       </c>
       <c r="K6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L6">
         <v>180</v>
@@ -3136,7 +3145,7 @@
         <v>1.75</v>
       </c>
       <c r="K7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L7">
         <v>180</v>
@@ -3178,7 +3187,7 @@
         <v>1.9047619047619</v>
       </c>
       <c r="K8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L8">
         <v>180</v>
@@ -3220,7 +3229,7 @@
         <v>2.04545454545455</v>
       </c>
       <c r="K9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L9">
         <v>180</v>
@@ -3262,7 +3271,7 @@
         <v>2.17391304347826</v>
       </c>
       <c r="K10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L10">
         <v>180</v>
@@ -3304,7 +3313,7 @@
         <v>2.29166666666667</v>
       </c>
       <c r="K11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L11">
         <v>180</v>
@@ -3331,7 +3340,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B1">
         <v>20</v>
@@ -3339,7 +3348,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3347,7 +3356,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3355,7 +3364,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -3363,7 +3372,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3371,7 +3380,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/Assets/Excel/excel.xlsx
+++ b/Assets/Excel/excel.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
   <si>
     <t>道具ID</t>
   </si>
@@ -236,10 +236,19 @@
     <t>黏胶</t>
   </si>
   <si>
+    <t>huangyou</t>
+  </si>
+  <si>
     <t>塞罗眼睛</t>
   </si>
   <si>
-    <t>初代奥特曼变身器</t>
+    <t>seruo</t>
+  </si>
+  <si>
+    <t>初代奥特曼</t>
+  </si>
+  <si>
+    <t>automan</t>
   </si>
   <si>
     <t>青蛙教练</t>
@@ -2457,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -2467,7 +2476,7 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C33" t="s">
@@ -2502,14 +2511,14 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="6" t="s">
         <v>66</v>
       </c>
       <c r="C34" t="s">
         <v>67</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E34">
         <v>0.2</v>
@@ -2537,14 +2546,14 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>68</v>
+      <c r="B35" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="C35" t="s">
         <v>47</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="E35">
         <v>0.12</v>
@@ -2572,14 +2581,14 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>69</v>
+      <c r="B36" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="E36">
         <v>0.28</v>
@@ -2607,14 +2616,14 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>70</v>
+      <c r="B37" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="C37" t="s">
         <v>35</v>
       </c>
       <c r="D37" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E37">
         <v>1.01</v>
@@ -2643,13 +2652,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
         <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E38">
         <v>0.73</v>
@@ -2678,13 +2687,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E39">
         <v>1.75</v>
@@ -2727,15 +2736,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B2">
         <v>15</v>
@@ -2743,7 +2752,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -2751,7 +2760,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2759,7 +2768,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B5">
         <v>0.18</v>
@@ -2767,7 +2776,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B6">
         <v>0.1</v>
@@ -2775,7 +2784,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -2783,7 +2792,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B8">
         <v>0.3</v>
@@ -2791,7 +2800,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -2799,7 +2808,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B10">
         <v>0.8</v>
@@ -2807,7 +2816,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -2815,7 +2824,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B12">
         <v>0.02</v>
@@ -2823,7 +2832,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2831,7 +2840,7 @@
     </row>
     <row r="14" ht="27" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -2839,7 +2848,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B15" s="1">
         <v>10</v>
@@ -2863,43 +2872,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2935,7 +2944,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L2">
         <v>180</v>
@@ -2977,7 +2986,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L3">
         <v>180</v>
@@ -3019,7 +3028,7 @@
         <v>1.05392156862745</v>
       </c>
       <c r="K4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L4">
         <v>180</v>
@@ -3061,7 +3070,7 @@
         <v>1.31944444444444</v>
       </c>
       <c r="K5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L5">
         <v>180</v>
@@ -3103,7 +3112,7 @@
         <v>1.55701754385965</v>
       </c>
       <c r="K6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L6">
         <v>180</v>
@@ -3145,7 +3154,7 @@
         <v>1.75</v>
       </c>
       <c r="K7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L7">
         <v>180</v>
@@ -3187,7 +3196,7 @@
         <v>1.9047619047619</v>
       </c>
       <c r="K8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L8">
         <v>180</v>
@@ -3229,7 +3238,7 @@
         <v>2.04545454545455</v>
       </c>
       <c r="K9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L9">
         <v>180</v>
@@ -3271,7 +3280,7 @@
         <v>2.17391304347826</v>
       </c>
       <c r="K10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L10">
         <v>180</v>
@@ -3313,7 +3322,7 @@
         <v>2.29166666666667</v>
       </c>
       <c r="K11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L11">
         <v>180</v>
@@ -3340,7 +3349,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B1">
         <v>20</v>
@@ -3348,7 +3357,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3356,7 +3365,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3364,7 +3373,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -3372,7 +3381,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3380,7 +3389,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/Assets/Excel/excel.xlsx
+++ b/Assets/Excel/excel.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="122">
   <si>
     <t>道具ID</t>
   </si>
@@ -200,12 +200,21 @@
     <t>破损的CD</t>
   </si>
   <si>
+    <t>brokencd</t>
+  </si>
+  <si>
     <t>香蕉皮</t>
   </si>
   <si>
+    <t>banana</t>
+  </si>
+  <si>
     <t>啤酒瓶</t>
   </si>
   <si>
+    <t>pijiu</t>
+  </si>
+  <si>
     <t>小布</t>
   </si>
   <si>
@@ -239,7 +248,7 @@
     <t>huangyou</t>
   </si>
   <si>
-    <t>塞罗眼睛</t>
+    <t>塞罗眼镜</t>
   </si>
   <si>
     <t>seruo</t>
@@ -2196,14 +2205,14 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>55</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E25">
         <v>0.07</v>
@@ -2231,14 +2240,14 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>56</v>
+      <c r="B26" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C26" t="s">
         <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E26">
         <v>0.12</v>
@@ -2266,14 +2275,14 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>57</v>
+      <c r="B27" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C27" t="s">
         <v>51</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E27">
         <v>0.42</v>
@@ -2302,7 +2311,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
         <v>35</v>
@@ -2337,7 +2346,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C29" t="s">
         <v>35</v>
@@ -2371,14 +2380,14 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>60</v>
+      <c r="B30" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E30">
         <v>4.6</v>
@@ -2407,7 +2416,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s">
         <v>37</v>
@@ -2442,7 +2451,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
         <v>51</v>
@@ -2476,14 +2485,14 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>64</v>
+      <c r="B33" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="C33" t="s">
         <v>35</v>
       </c>
       <c r="D33" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E33">
         <v>1.52</v>
@@ -2512,13 +2521,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E34">
         <v>0.2</v>
@@ -2547,13 +2556,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
         <v>47</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E35">
         <v>0.12</v>
@@ -2582,13 +2591,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E36">
         <v>0.28</v>
@@ -2616,14 +2625,14 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>73</v>
+      <c r="B37" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="C37" t="s">
         <v>35</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E37">
         <v>1.01</v>
@@ -2651,14 +2660,14 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>75</v>
+      <c r="B38" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="C38" t="s">
         <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E38">
         <v>0.73</v>
@@ -2687,13 +2696,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E39">
         <v>1.75</v>
@@ -2736,15 +2745,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B2">
         <v>15</v>
@@ -2752,7 +2761,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -2760,7 +2769,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2768,7 +2777,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B5">
         <v>0.18</v>
@@ -2776,7 +2785,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B6">
         <v>0.1</v>
@@ -2784,7 +2793,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -2792,7 +2801,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B8">
         <v>0.3</v>
@@ -2800,7 +2809,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -2808,7 +2817,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B10">
         <v>0.8</v>
@@ -2816,7 +2825,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -2824,7 +2833,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B12">
         <v>0.02</v>
@@ -2832,7 +2841,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2840,7 +2849,7 @@
     </row>
     <row r="14" ht="27" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -2848,7 +2857,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B15" s="1">
         <v>10</v>
@@ -2872,43 +2881,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2944,7 +2953,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L2">
         <v>180</v>
@@ -2986,7 +2995,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L3">
         <v>180</v>
@@ -3028,7 +3037,7 @@
         <v>1.05392156862745</v>
       </c>
       <c r="K4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L4">
         <v>180</v>
@@ -3070,7 +3079,7 @@
         <v>1.31944444444444</v>
       </c>
       <c r="K5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L5">
         <v>180</v>
@@ -3112,7 +3121,7 @@
         <v>1.55701754385965</v>
       </c>
       <c r="K6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L6">
         <v>180</v>
@@ -3154,7 +3163,7 @@
         <v>1.75</v>
       </c>
       <c r="K7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L7">
         <v>180</v>
@@ -3196,7 +3205,7 @@
         <v>1.9047619047619</v>
       </c>
       <c r="K8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L8">
         <v>180</v>
@@ -3238,7 +3247,7 @@
         <v>2.04545454545455</v>
       </c>
       <c r="K9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L9">
         <v>180</v>
@@ -3280,7 +3289,7 @@
         <v>2.17391304347826</v>
       </c>
       <c r="K10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L10">
         <v>180</v>
@@ -3322,7 +3331,7 @@
         <v>2.29166666666667</v>
       </c>
       <c r="K11" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L11">
         <v>180</v>
@@ -3349,7 +3358,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B1">
         <v>20</v>
@@ -3357,7 +3366,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3365,7 +3374,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3373,7 +3382,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -3381,7 +3390,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3389,7 +3398,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/Assets/Excel/excel.xlsx
+++ b/Assets/Excel/excel.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="124">
   <si>
     <t>道具ID</t>
   </si>
@@ -71,67 +71,73 @@
     <t>木头</t>
   </si>
   <si>
+    <t>xiaoren</t>
+  </si>
+  <si>
+    <t>冰红茶</t>
+  </si>
+  <si>
+    <t>塑料</t>
+  </si>
+  <si>
+    <t>man</t>
+  </si>
+  <si>
+    <t>飞碟</t>
+  </si>
+  <si>
+    <t>合金</t>
+  </si>
+  <si>
+    <t>nokia</t>
+  </si>
+  <si>
+    <t>旧水管（弯、短）</t>
+  </si>
+  <si>
+    <t>金属</t>
+  </si>
+  <si>
+    <t>shuiguan</t>
+  </si>
+  <si>
+    <t>旧水管（弯、长）</t>
+  </si>
+  <si>
+    <t>shuiguan2</t>
+  </si>
+  <si>
+    <t>旧水管（直、短）</t>
+  </si>
+  <si>
+    <t>xiaomei</t>
+  </si>
+  <si>
+    <t>旧水管（直、长）</t>
+  </si>
+  <si>
     <t>huh</t>
   </si>
   <si>
-    <t>冰红茶</t>
-  </si>
-  <si>
-    <t>塑料</t>
-  </si>
-  <si>
-    <t>man</t>
-  </si>
-  <si>
-    <t>飞碟</t>
-  </si>
-  <si>
-    <t>合金</t>
-  </si>
-  <si>
-    <t>nokia</t>
-  </si>
-  <si>
-    <t>旧水管（弯、短）</t>
-  </si>
-  <si>
-    <t>金属</t>
-  </si>
-  <si>
-    <t>shuiguan</t>
-  </si>
-  <si>
-    <t>旧水管（弯、长）</t>
+    <t>烂靴子</t>
+  </si>
+  <si>
+    <t>布</t>
+  </si>
+  <si>
+    <t>船锚玩具</t>
+  </si>
+  <si>
+    <t>chuanmao</t>
+  </si>
+  <si>
+    <t>一罐鱼饵</t>
+  </si>
+  <si>
+    <t>假饵</t>
   </si>
   <si>
     <t>xiaobu</t>
-  </si>
-  <si>
-    <t>旧水管（直、短）</t>
-  </si>
-  <si>
-    <t>xiaomei</t>
-  </si>
-  <si>
-    <t>旧水管（直、长）</t>
-  </si>
-  <si>
-    <t>烂靴子</t>
-  </si>
-  <si>
-    <t>布</t>
-  </si>
-  <si>
-    <t>船锚玩具</t>
-  </si>
-  <si>
-    <t>chuanmao</t>
-  </si>
-  <si>
-    <t>一罐鱼饵</t>
-  </si>
-  <si>
-    <t>假饵</t>
   </si>
   <si>
     <t>外星人</t>
@@ -1035,10 +1041,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1358,6 +1364,7 @@
   <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
+    <col min="2" max="2" width="18.3583333333333" customWidth="1"/>
     <col min="9" max="9" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1470,7 +1477,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C4" t="s">
@@ -1575,7 +1582,7 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
@@ -1610,14 +1617,14 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E8">
         <v>0.73</v>
@@ -1645,11 +1652,11 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>28</v>
+      <c r="B9" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -1681,13 +1688,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10">
         <v>0.2</v>
@@ -1715,8 +1722,8 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>32</v>
+      <c r="B11" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
@@ -1750,14 +1757,14 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>33</v>
+      <c r="B12" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E12">
         <v>0.2</v>
@@ -1785,11 +1792,11 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>34</v>
+      <c r="B13" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
@@ -1821,13 +1828,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E14">
         <v>0.73</v>
@@ -1856,13 +1863,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
         <v>39</v>
       </c>
-      <c r="C15" t="s">
-        <v>37</v>
-      </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E15">
         <v>0.73</v>
@@ -1891,13 +1898,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E16">
         <v>0.73</v>
@@ -1926,13 +1933,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E17">
         <v>0.73</v>
@@ -1961,7 +1968,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
         <v>21</v>
@@ -1995,11 +2002,11 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>46</v>
+      <c r="B19" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
@@ -2030,14 +2037,14 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>48</v>
+      <c r="B20" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E20">
         <v>0.07</v>
@@ -2065,8 +2072,8 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>49</v>
+      <c r="B21" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
@@ -2100,11 +2107,11 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>50</v>
+      <c r="B22" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
         <v>19</v>
@@ -2135,8 +2142,8 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>52</v>
+      <c r="B23" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -2170,14 +2177,14 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>53</v>
+      <c r="B24" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E24">
         <v>0.02</v>
@@ -2205,14 +2212,14 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>55</v>
+      <c r="B25" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E25">
         <v>0.07</v>
@@ -2240,14 +2247,14 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>57</v>
+      <c r="B26" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E26">
         <v>0.12</v>
@@ -2275,14 +2282,14 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>59</v>
+      <c r="B27" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E27">
         <v>0.42</v>
@@ -2311,13 +2318,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" t="s">
         <v>35</v>
-      </c>
-      <c r="D28" t="s">
-        <v>24</v>
       </c>
       <c r="E28">
         <v>4.6</v>
@@ -2346,10 +2353,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s">
         <v>26</v>
@@ -2381,13 +2388,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E30">
         <v>4.6</v>
@@ -2415,11 +2422,11 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>65</v>
+      <c r="B31" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
@@ -2450,14 +2457,14 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>66</v>
+      <c r="B32" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E32">
         <v>0.42</v>
@@ -2486,13 +2493,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E33">
         <v>1.52</v>
@@ -2521,13 +2528,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D34" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E34">
         <v>0.2</v>
@@ -2556,13 +2563,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E35">
         <v>0.12</v>
@@ -2591,13 +2598,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E36">
         <v>0.28</v>
@@ -2626,13 +2633,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E37">
         <v>1.01</v>
@@ -2661,13 +2668,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E38">
         <v>0.73</v>
@@ -2696,13 +2703,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E39">
         <v>1.75</v>
@@ -2745,15 +2752,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B2">
         <v>15</v>
@@ -2761,7 +2768,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -2769,7 +2776,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2777,7 +2784,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B5">
         <v>0.18</v>
@@ -2785,7 +2792,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B6">
         <v>0.1</v>
@@ -2793,7 +2800,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -2801,7 +2808,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8">
         <v>0.3</v>
@@ -2809,7 +2816,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -2817,7 +2824,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B10">
         <v>0.8</v>
@@ -2825,7 +2832,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -2833,7 +2840,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12">
         <v>0.02</v>
@@ -2841,7 +2848,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2849,7 +2856,7 @@
     </row>
     <row r="14" ht="27" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -2857,7 +2864,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B15" s="1">
         <v>10</v>
@@ -2881,43 +2888,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2953,7 +2960,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L2">
         <v>180</v>
@@ -2995,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L3">
         <v>180</v>
@@ -3037,7 +3044,7 @@
         <v>1.05392156862745</v>
       </c>
       <c r="K4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="L4">
         <v>180</v>
@@ -3079,7 +3086,7 @@
         <v>1.31944444444444</v>
       </c>
       <c r="K5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L5">
         <v>180</v>
@@ -3121,7 +3128,7 @@
         <v>1.55701754385965</v>
       </c>
       <c r="K6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L6">
         <v>180</v>
@@ -3163,7 +3170,7 @@
         <v>1.75</v>
       </c>
       <c r="K7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L7">
         <v>180</v>
@@ -3205,7 +3212,7 @@
         <v>1.9047619047619</v>
       </c>
       <c r="K8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L8">
         <v>180</v>
@@ -3247,7 +3254,7 @@
         <v>2.04545454545455</v>
       </c>
       <c r="K9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L9">
         <v>180</v>
@@ -3289,7 +3296,7 @@
         <v>2.17391304347826</v>
       </c>
       <c r="K10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L10">
         <v>180</v>
@@ -3331,7 +3338,7 @@
         <v>2.29166666666667</v>
       </c>
       <c r="K11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L11">
         <v>180</v>
@@ -3358,7 +3365,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B1">
         <v>20</v>
@@ -3366,7 +3373,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3374,7 +3381,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3382,7 +3389,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -3390,7 +3397,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3398,7 +3405,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/Assets/Excel/excel.xlsx
+++ b/Assets/Excel/excel.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="126">
   <si>
     <t>道具ID</t>
   </si>
@@ -197,10 +197,16 @@
     <t>浮木</t>
   </si>
   <si>
+    <t>fumu</t>
+  </si>
+  <si>
     <t>湿透的报纸</t>
   </si>
   <si>
     <t>纸张</t>
+  </si>
+  <si>
+    <t>baozhi</t>
   </si>
   <si>
     <t>破损的CD</t>
@@ -2142,14 +2148,14 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E23">
         <v>0.42</v>
@@ -2177,14 +2183,14 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>55</v>
+      <c r="B24" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E24">
         <v>0.02</v>
@@ -2213,13 +2219,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E25">
         <v>0.07</v>
@@ -2248,13 +2254,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
         <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E26">
         <v>0.12</v>
@@ -2283,13 +2289,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s">
         <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E27">
         <v>0.42</v>
@@ -2318,7 +2324,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
         <v>37</v>
@@ -2353,7 +2359,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
         <v>37</v>
@@ -2388,13 +2394,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
         <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E30">
         <v>4.6</v>
@@ -2423,7 +2429,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s">
         <v>39</v>
@@ -2458,7 +2464,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
         <v>53</v>
@@ -2493,13 +2499,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
         <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E33">
         <v>1.52</v>
@@ -2528,13 +2534,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E34">
         <v>0.2</v>
@@ -2563,13 +2569,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C35" t="s">
         <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E35">
         <v>0.12</v>
@@ -2598,13 +2604,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E36">
         <v>0.28</v>
@@ -2633,13 +2639,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C37" t="s">
         <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E37">
         <v>1.01</v>
@@ -2668,13 +2674,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E38">
         <v>0.73</v>
@@ -2703,13 +2709,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E39">
         <v>1.75</v>
@@ -2752,15 +2758,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B2">
         <v>15</v>
@@ -2768,7 +2774,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -2776,7 +2782,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2784,7 +2790,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B5">
         <v>0.18</v>
@@ -2792,7 +2798,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B6">
         <v>0.1</v>
@@ -2800,7 +2806,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -2808,7 +2814,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B8">
         <v>0.3</v>
@@ -2816,7 +2822,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -2824,7 +2830,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B10">
         <v>0.8</v>
@@ -2832,7 +2838,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -2840,7 +2846,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B12">
         <v>0.02</v>
@@ -2848,7 +2854,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2856,7 +2862,7 @@
     </row>
     <row r="14" ht="27" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -2864,7 +2870,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B15" s="1">
         <v>10</v>
@@ -2888,43 +2894,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2960,7 +2966,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="L2">
         <v>180</v>
@@ -3002,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L3">
         <v>180</v>
@@ -3044,7 +3050,7 @@
         <v>1.05392156862745</v>
       </c>
       <c r="K4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L4">
         <v>180</v>
@@ -3086,7 +3092,7 @@
         <v>1.31944444444444</v>
       </c>
       <c r="K5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L5">
         <v>180</v>
@@ -3128,7 +3134,7 @@
         <v>1.55701754385965</v>
       </c>
       <c r="K6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L6">
         <v>180</v>
@@ -3170,7 +3176,7 @@
         <v>1.75</v>
       </c>
       <c r="K7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L7">
         <v>180</v>
@@ -3212,7 +3218,7 @@
         <v>1.9047619047619</v>
       </c>
       <c r="K8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L8">
         <v>180</v>
@@ -3254,7 +3260,7 @@
         <v>2.04545454545455</v>
       </c>
       <c r="K9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L9">
         <v>180</v>
@@ -3296,7 +3302,7 @@
         <v>2.17391304347826</v>
       </c>
       <c r="K10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L10">
         <v>180</v>
@@ -3338,7 +3344,7 @@
         <v>2.29166666666667</v>
       </c>
       <c r="K11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L11">
         <v>180</v>
@@ -3365,7 +3371,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B1">
         <v>20</v>
@@ -3373,7 +3379,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3381,7 +3387,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3389,7 +3395,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -3397,7 +3403,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3405,7 +3411,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/Assets/Excel/excel.xlsx
+++ b/Assets/Excel/excel.xlsx
@@ -1036,7 +1036,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1051,9 +1051,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1508,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1613,7 +1610,7 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1648,7 +1645,7 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -1683,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -1753,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -1788,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -1823,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -2033,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -2068,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -2103,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -2138,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -2218,7 +2215,7 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C25" t="s">
@@ -2253,7 +2250,7 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C26" t="s">
@@ -2288,7 +2285,7 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C27" t="s">
@@ -2393,7 +2390,7 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C30" t="s">
@@ -2498,7 +2495,7 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C33" t="s">
@@ -2533,7 +2530,7 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C34" t="s">
@@ -2568,7 +2565,7 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C35" t="s">
@@ -2603,7 +2600,7 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C36" t="s">
@@ -2638,7 +2635,7 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C37" t="s">
@@ -2673,7 +2670,7 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C38" t="s">

--- a/Assets/Excel/excel.xlsx
+++ b/Assets/Excel/excel.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="129">
   <si>
     <t>道具ID</t>
   </si>
@@ -89,102 +89,111 @@
     <t>合金</t>
   </si>
   <si>
+    <t>feidie</t>
+  </si>
+  <si>
+    <t>旧水管（弯、短）</t>
+  </si>
+  <si>
+    <t>金属</t>
+  </si>
+  <si>
+    <t>shuiguan</t>
+  </si>
+  <si>
+    <t>旧水管（弯、长）</t>
+  </si>
+  <si>
+    <t>shuiguan2</t>
+  </si>
+  <si>
+    <t>旧水管（直、短）</t>
+  </si>
+  <si>
+    <t>shuiguan3</t>
+  </si>
+  <si>
+    <t>旧水管（直、长）</t>
+  </si>
+  <si>
+    <t>shuiguan4</t>
+  </si>
+  <si>
+    <t>烂靴子</t>
+  </si>
+  <si>
+    <t>布</t>
+  </si>
+  <si>
+    <t>船锚玩具</t>
+  </si>
+  <si>
+    <t>chuanmao</t>
+  </si>
+  <si>
+    <t>一罐鱼饵</t>
+  </si>
+  <si>
+    <t>假饵</t>
+  </si>
+  <si>
+    <t>xiaobu</t>
+  </si>
+  <si>
+    <t>外星人</t>
+  </si>
+  <si>
+    <t>生物</t>
+  </si>
+  <si>
+    <t>xiaomei</t>
+  </si>
+  <si>
+    <t>字母C</t>
+  </si>
+  <si>
+    <t>文字</t>
+  </si>
+  <si>
+    <t>cigaC</t>
+  </si>
+  <si>
+    <t>字母I</t>
+  </si>
+  <si>
+    <t>cigaI</t>
+  </si>
+  <si>
+    <t>字母G</t>
+  </si>
+  <si>
+    <t>cigaG</t>
+  </si>
+  <si>
+    <t>字母A</t>
+  </si>
+  <si>
+    <t>cigaA</t>
+  </si>
+  <si>
+    <t>手机</t>
+  </si>
+  <si>
     <t>nokia</t>
   </si>
   <si>
-    <t>旧水管（弯、短）</t>
-  </si>
-  <si>
-    <t>金属</t>
-  </si>
-  <si>
-    <t>shuiguan</t>
-  </si>
-  <si>
-    <t>旧水管（弯、长）</t>
-  </si>
-  <si>
-    <t>shuiguan2</t>
-  </si>
-  <si>
-    <t>旧水管（直、短）</t>
-  </si>
-  <si>
-    <t>xiaomei</t>
-  </si>
-  <si>
-    <t>旧水管（直、长）</t>
+    <t>奇异物质</t>
+  </si>
+  <si>
+    <t>神秘物质</t>
+  </si>
+  <si>
+    <t>工牌</t>
   </si>
   <si>
     <t>huh</t>
   </si>
   <si>
-    <t>烂靴子</t>
-  </si>
-  <si>
-    <t>布</t>
-  </si>
-  <si>
-    <t>船锚玩具</t>
-  </si>
-  <si>
-    <t>chuanmao</t>
-  </si>
-  <si>
-    <t>一罐鱼饵</t>
-  </si>
-  <si>
-    <t>假饵</t>
-  </si>
-  <si>
-    <t>xiaobu</t>
-  </si>
-  <si>
-    <t>外星人</t>
-  </si>
-  <si>
-    <t>生物</t>
-  </si>
-  <si>
-    <t>字母C</t>
-  </si>
-  <si>
-    <t>文字</t>
-  </si>
-  <si>
-    <t>cigaC</t>
-  </si>
-  <si>
-    <t>字母I</t>
-  </si>
-  <si>
-    <t>cigaI</t>
-  </si>
-  <si>
-    <t>字母G</t>
-  </si>
-  <si>
-    <t>cigaG</t>
-  </si>
-  <si>
-    <t>字母A</t>
-  </si>
-  <si>
-    <t>cigaA</t>
-  </si>
-  <si>
-    <t>手机</t>
-  </si>
-  <si>
-    <t>奇异物质</t>
-  </si>
-  <si>
-    <t>神秘物质</t>
-  </si>
-  <si>
-    <t>工牌</t>
-  </si>
-  <si>
     <t>自行车</t>
   </si>
   <si>
@@ -242,7 +251,7 @@
     <t>“区”</t>
   </si>
   <si>
-    <t>碎玻璃</t>
+    <t>Uhu</t>
   </si>
   <si>
     <t>西瓜</t>
@@ -1480,7 +1489,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C4" t="s">
@@ -1505,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1585,7 +1594,7 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
@@ -1610,7 +1619,7 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1620,7 +1629,7 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
@@ -1645,13 +1654,13 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="K8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" ht="13" customHeight="1" spans="1:11">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1802,7 +1811,7 @@
         <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E13">
         <v>0.42</v>
@@ -1831,13 +1840,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14">
         <v>0.73</v>
@@ -1866,13 +1875,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15">
         <v>0.73</v>
@@ -1901,13 +1910,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E16">
         <v>0.73</v>
@@ -1936,13 +1945,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17">
         <v>0.73</v>
@@ -1971,13 +1980,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="E18">
         <v>0.42</v>
@@ -2006,13 +2015,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E19">
         <v>29</v>
@@ -2041,13 +2050,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E20">
         <v>0.07</v>
@@ -2076,7 +2085,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
@@ -2111,13 +2120,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="E22">
         <v>0.28</v>
@@ -2146,13 +2155,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E23">
         <v>0.42</v>
@@ -2181,13 +2190,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E24">
         <v>0.02</v>
@@ -2216,13 +2225,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E25">
         <v>0.07</v>
@@ -2251,13 +2260,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
         <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E26">
         <v>0.12</v>
@@ -2286,13 +2295,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E27">
         <v>0.42</v>
@@ -2321,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
         <v>37</v>
@@ -2356,13 +2365,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
         <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E29">
         <v>2.64</v>
@@ -2391,13 +2400,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
         <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E30">
         <v>4.6</v>
@@ -2426,13 +2435,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E31">
         <v>1.27</v>
@@ -2460,14 +2469,14 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>70</v>
+      <c r="B32" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" t="s">
         <v>53</v>
-      </c>
-      <c r="D32" t="s">
-        <v>28</v>
       </c>
       <c r="E32">
         <v>0.42</v>
@@ -2496,13 +2505,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s">
         <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E33">
         <v>1.52</v>
@@ -2531,13 +2540,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E34">
         <v>0.2</v>
@@ -2566,13 +2575,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D35" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E35">
         <v>0.12</v>
@@ -2601,13 +2610,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E36">
         <v>0.28</v>
@@ -2636,13 +2645,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C37" t="s">
         <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E37">
         <v>1.01</v>
@@ -2671,13 +2680,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C38" t="s">
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E38">
         <v>0.73</v>
@@ -2706,13 +2715,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E39">
         <v>1.75</v>
@@ -2755,15 +2764,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B2">
         <v>15</v>
@@ -2771,7 +2780,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -2779,7 +2788,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2787,7 +2796,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B5">
         <v>0.18</v>
@@ -2795,7 +2804,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B6">
         <v>0.1</v>
@@ -2803,7 +2812,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -2811,7 +2820,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B8">
         <v>0.3</v>
@@ -2819,7 +2828,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -2827,7 +2836,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B10">
         <v>0.8</v>
@@ -2835,7 +2844,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -2843,7 +2852,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B12">
         <v>0.02</v>
@@ -2851,7 +2860,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2859,7 +2868,7 @@
     </row>
     <row r="14" ht="27" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -2867,7 +2876,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B15" s="1">
         <v>10</v>
@@ -2891,43 +2900,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="J1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2963,7 +2972,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L2">
         <v>180</v>
@@ -3005,7 +3014,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L3">
         <v>180</v>
@@ -3047,7 +3056,7 @@
         <v>1.05392156862745</v>
       </c>
       <c r="K4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L4">
         <v>180</v>
@@ -3089,7 +3098,7 @@
         <v>1.31944444444444</v>
       </c>
       <c r="K5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L5">
         <v>180</v>
@@ -3131,7 +3140,7 @@
         <v>1.55701754385965</v>
       </c>
       <c r="K6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L6">
         <v>180</v>
@@ -3173,7 +3182,7 @@
         <v>1.75</v>
       </c>
       <c r="K7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L7">
         <v>180</v>
@@ -3215,7 +3224,7 @@
         <v>1.9047619047619</v>
       </c>
       <c r="K8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L8">
         <v>180</v>
@@ -3257,7 +3266,7 @@
         <v>2.04545454545455</v>
       </c>
       <c r="K9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L9">
         <v>180</v>
@@ -3299,7 +3308,7 @@
         <v>2.17391304347826</v>
       </c>
       <c r="K10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L10">
         <v>180</v>
@@ -3341,7 +3350,7 @@
         <v>2.29166666666667</v>
       </c>
       <c r="K11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L11">
         <v>180</v>
@@ -3368,7 +3377,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B1">
         <v>20</v>
@@ -3376,7 +3385,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3384,7 +3393,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3392,7 +3401,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -3400,7 +3409,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3408,7 +3417,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B6">
         <v>1</v>

--- a/Assets/Excel/excel.xlsx
+++ b/Assets/Excel/excel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowHeight="17775" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
@@ -2999,7 +2999,7 @@
         <v>12</v>
       </c>
       <c r="F3">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="G3">
         <v>32</v>
@@ -3041,7 +3041,7 @@
         <v>14</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G4">
         <v>34</v>
@@ -3083,7 +3083,7 @@
         <v>16</v>
       </c>
       <c r="F5">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="G5">
         <v>36</v>
@@ -3125,7 +3125,7 @@
         <v>18</v>
       </c>
       <c r="F6">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>38</v>
@@ -3167,7 +3167,7 @@
         <v>20</v>
       </c>
       <c r="F7">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="G7">
         <v>40</v>
@@ -3209,7 +3209,7 @@
         <v>22</v>
       </c>
       <c r="F8">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="G8">
         <v>42</v>
@@ -3251,7 +3251,7 @@
         <v>24</v>
       </c>
       <c r="F9">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="G9">
         <v>44</v>
@@ -3293,7 +3293,7 @@
         <v>26</v>
       </c>
       <c r="F10">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="G10">
         <v>46</v>
@@ -3335,7 +3335,7 @@
         <v>28</v>
       </c>
       <c r="F11">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="G11">
         <v>48</v>

--- a/Assets/Excel/excel.xlsx
+++ b/Assets/Excel/excel.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ciga\2026CIGA\Assets\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19DD83ED-CC06-456E-8736-8697F389176C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17775" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
@@ -30,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="130">
   <si>
     <t>道具ID</t>
   </si>
@@ -329,107 +335,107 @@
     <t>血量系数。物品健康值转换为连接最大血量的倍率。</t>
   </si>
   <si>
+    <t>海底 Unity 物理材质弹性系数。</t>
+  </si>
+  <si>
+    <t>是否显示连接血量调试信息。1 显示，0 隐藏。</t>
+  </si>
+  <si>
+    <t>物品质量系数。物品重量转换为 Unity Rigidbody2D.mass 的全局倍率。</t>
+  </si>
+  <si>
+    <t>入水初速度</t>
+  </si>
+  <si>
+    <t>关卡ID</t>
+  </si>
+  <si>
+    <t>船重量（展示用）</t>
+  </si>
+  <si>
+    <t>初始距离</t>
+  </si>
+  <si>
+    <t>最大速度</t>
+  </si>
+  <si>
+    <t>关卡基础拉力</t>
+  </si>
+  <si>
+    <t>向右横力</t>
+  </si>
+  <si>
+    <t>随机道具最低数量</t>
+  </si>
+  <si>
+    <t>最低道具总重量</t>
+  </si>
+  <si>
+    <t>推荐重量（千克）</t>
+  </si>
+  <si>
+    <t>道具重量系数</t>
+  </si>
+  <si>
+    <t>风暴级别</t>
+  </si>
+  <si>
+    <t>拼凑时间（秒）</t>
+  </si>
+  <si>
+    <t>水面张力</t>
+  </si>
+  <si>
+    <t>低级</t>
+  </si>
+  <si>
+    <t>低中</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>中高</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>坚持时间(秒）</t>
+  </si>
+  <si>
+    <t>掉落速度（m/s)</t>
+  </si>
+  <si>
+    <t>受力系数</t>
+  </si>
+  <si>
+    <t>阈值系数</t>
+  </si>
+  <si>
+    <t>伤害系数</t>
+  </si>
+  <si>
+    <t>血量系数</t>
+  </si>
+  <si>
+    <t>海底 Unity 物理材质摩擦系数。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>摩擦系数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>防御转关节频率系数。防御越高，Unity FixedJoint2D 越硬。</t>
-  </si>
-  <si>
-    <t>海底 Unity 物理材质摩擦系数。</t>
-  </si>
-  <si>
-    <t>海底 Unity 物理材质弹性系数。</t>
-  </si>
-  <si>
-    <t>是否显示连接血量调试信息。1 显示，0 隐藏。</t>
-  </si>
-  <si>
-    <t>物品质量系数。物品重量转换为 Unity Rigidbody2D.mass 的全局倍率。</t>
-  </si>
-  <si>
-    <t>入水初速度</t>
-  </si>
-  <si>
-    <t>关卡ID</t>
-  </si>
-  <si>
-    <t>船重量（展示用）</t>
-  </si>
-  <si>
-    <t>初始距离</t>
-  </si>
-  <si>
-    <t>最大速度</t>
-  </si>
-  <si>
-    <t>关卡基础拉力</t>
-  </si>
-  <si>
-    <t>向右横力</t>
-  </si>
-  <si>
-    <t>随机道具最低数量</t>
-  </si>
-  <si>
-    <t>最低道具总重量</t>
-  </si>
-  <si>
-    <t>推荐重量（千克）</t>
-  </si>
-  <si>
-    <t>道具重量系数</t>
-  </si>
-  <si>
-    <t>风暴级别</t>
-  </si>
-  <si>
-    <t>拼凑时间（秒）</t>
-  </si>
-  <si>
-    <t>水面张力</t>
-  </si>
-  <si>
-    <t>低级</t>
-  </si>
-  <si>
-    <t>低中</t>
-  </si>
-  <si>
-    <t>中</t>
-  </si>
-  <si>
-    <t>中高</t>
-  </si>
-  <si>
-    <t>高</t>
-  </si>
-  <si>
-    <t>坚持时间(秒）</t>
-  </si>
-  <si>
-    <t>掉落速度（m/s)</t>
-  </si>
-  <si>
-    <t>受力系数</t>
-  </si>
-  <si>
-    <t>阈值系数</t>
-  </si>
-  <si>
-    <t>伤害系数</t>
-  </si>
-  <si>
-    <t>血量系数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -441,155 +447,27 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -602,194 +480,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -797,256 +489,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1056,68 +506,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1367,20 +776,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="18.3583333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="18.375" customWidth="1"/>
+    <col min="10" max="10" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1402,24 +811,27 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
@@ -1438,19 +850,22 @@
         <v>10</v>
       </c>
       <c r="H2">
+        <v>0.3</v>
+      </c>
+      <c r="I2">
         <v>2</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>331</v>
       </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1473,23 +888,26 @@
         <v>12</v>
       </c>
       <c r="H3">
+        <v>0.15</v>
+      </c>
+      <c r="I3">
         <v>3</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>285</v>
       </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>17</v>
       </c>
       <c r="C4" t="s">
@@ -1499,7 +917,7 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F4">
         <v>416</v>
@@ -1508,19 +926,22 @@
         <v>60</v>
       </c>
       <c r="H4">
+        <v>0.15</v>
+      </c>
+      <c r="I4">
         <v>6</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
       <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>176</v>
       </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1543,23 +964,26 @@
         <v>12</v>
       </c>
       <c r="H5">
+        <v>0.2</v>
+      </c>
+      <c r="I5">
         <v>2</v>
       </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="J5">
-        <v>285</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>150</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
@@ -1578,23 +1002,26 @@
         <v>24</v>
       </c>
       <c r="H6">
+        <v>0.2</v>
+      </c>
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
       <c r="J6">
-        <v>256</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>150</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
@@ -1613,23 +1040,26 @@
         <v>12</v>
       </c>
       <c r="H7">
+        <v>0.2</v>
+      </c>
+      <c r="I7">
         <v>2</v>
       </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
       <c r="J7">
-        <v>285</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>150</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
@@ -1648,23 +1078,26 @@
         <v>24</v>
       </c>
       <c r="H8">
+        <v>0.2</v>
+      </c>
+      <c r="I8">
         <v>4</v>
       </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
       <c r="J8">
-        <v>256</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="13" customHeight="1" spans="1:11">
+        <v>150</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
@@ -1683,19 +1116,22 @@
         <v>6</v>
       </c>
       <c r="H9">
+        <v>0.3</v>
+      </c>
+      <c r="I9">
         <v>3</v>
       </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1718,23 +1154,26 @@
         <v>8</v>
       </c>
       <c r="H10">
+        <v>0.15</v>
+      </c>
+      <c r="I10">
         <v>2</v>
       </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
       <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
         <v>331</v>
       </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C11" t="s">
@@ -1753,23 +1192,26 @@
         <v>12</v>
       </c>
       <c r="H11">
+        <v>0.2</v>
+      </c>
+      <c r="I11">
         <v>2</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C12" t="s">
@@ -1788,23 +1230,26 @@
         <v>4</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C13" t="s">
@@ -1823,19 +1268,22 @@
         <v>12</v>
       </c>
       <c r="H13">
+        <v>0.25</v>
+      </c>
+      <c r="I13">
         <v>3</v>
       </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1858,19 +1306,22 @@
         <v>18</v>
       </c>
       <c r="H14">
+        <v>0.15</v>
+      </c>
+      <c r="I14">
         <v>3</v>
       </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1893,19 +1344,22 @@
         <v>18</v>
       </c>
       <c r="H15">
+        <v>0.15</v>
+      </c>
+      <c r="I15">
         <v>3</v>
       </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1928,19 +1382,22 @@
         <v>18</v>
       </c>
       <c r="H16">
+        <v>0.15</v>
+      </c>
+      <c r="I16">
         <v>3</v>
       </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1963,19 +1420,22 @@
         <v>18</v>
       </c>
       <c r="H17">
+        <v>0.15</v>
+      </c>
+      <c r="I17">
         <v>3</v>
       </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1998,23 +1458,26 @@
         <v>12</v>
       </c>
       <c r="H18">
+        <v>0.2</v>
+      </c>
+      <c r="I18">
         <v>2</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
       <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
         <v>285</v>
       </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C19" t="s">
@@ -2033,23 +1496,26 @@
         <v>30</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C20" t="s">
@@ -2059,7 +1525,7 @@
         <v>53</v>
       </c>
       <c r="E20">
-        <v>0.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F20">
         <v>60</v>
@@ -2068,23 +1534,26 @@
         <v>8</v>
       </c>
       <c r="H20">
+        <v>0.1</v>
+      </c>
+      <c r="I20">
         <v>2</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C21" t="s">
@@ -2103,23 +1572,26 @@
         <v>30</v>
       </c>
       <c r="H21">
+        <v>0.2</v>
+      </c>
+      <c r="I21">
         <v>5</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C22" t="s">
@@ -2129,7 +1601,7 @@
         <v>49</v>
       </c>
       <c r="E22">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="F22">
         <v>13</v>
@@ -2138,23 +1610,26 @@
         <v>6</v>
       </c>
       <c r="H22">
+        <v>0.1</v>
+      </c>
+      <c r="I22">
         <v>2</v>
       </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" t="s">
         <v>57</v>
       </c>
       <c r="C23" t="s">
@@ -2173,23 +1648,26 @@
         <v>15</v>
       </c>
       <c r="H23">
+        <v>0.3</v>
+      </c>
+      <c r="I23">
         <v>3</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
       <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
         <v>285</v>
       </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" t="s">
         <v>59</v>
       </c>
       <c r="C24" t="s">
@@ -2208,23 +1686,26 @@
         <v>2</v>
       </c>
       <c r="H24">
+        <v>0.4</v>
+      </c>
+      <c r="I24">
         <v>4</v>
       </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
       <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
         <v>524</v>
       </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" t="s">
         <v>62</v>
       </c>
       <c r="C25" t="s">
@@ -2234,7 +1715,7 @@
         <v>63</v>
       </c>
       <c r="E25">
-        <v>0.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F25">
         <v>60</v>
@@ -2243,23 +1724,26 @@
         <v>4</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
         <v>407</v>
       </c>
-      <c r="K25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" t="s">
         <v>64</v>
       </c>
       <c r="C26" t="s">
@@ -2278,23 +1762,26 @@
         <v>8</v>
       </c>
       <c r="H26">
+        <v>0.1</v>
+      </c>
+      <c r="I26">
         <v>2</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
       <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
         <v>366</v>
       </c>
-      <c r="K26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="L26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" t="s">
         <v>66</v>
       </c>
       <c r="C27" t="s">
@@ -2313,19 +1800,22 @@
         <v>9</v>
       </c>
       <c r="H27">
+        <v>0.1</v>
+      </c>
+      <c r="I27">
         <v>3</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
       <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
         <v>285</v>
       </c>
-      <c r="K27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="L27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2339,7 +1829,7 @@
         <v>35</v>
       </c>
       <c r="E28">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F28">
         <v>84</v>
@@ -2348,19 +1838,22 @@
         <v>16</v>
       </c>
       <c r="H28">
+        <v>0.25</v>
+      </c>
+      <c r="I28">
         <v>4</v>
       </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
       <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
         <v>397</v>
       </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="L28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2383,23 +1876,26 @@
         <v>16</v>
       </c>
       <c r="H29">
+        <v>0.25</v>
+      </c>
+      <c r="I29">
         <v>4</v>
       </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
       <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
         <v>419</v>
       </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="L29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" t="s">
         <v>70</v>
       </c>
       <c r="C30" t="s">
@@ -2409,7 +1905,7 @@
         <v>71</v>
       </c>
       <c r="E30">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F30">
         <v>84</v>
@@ -2418,23 +1914,26 @@
         <v>20</v>
       </c>
       <c r="H30">
+        <v>0.25</v>
+      </c>
+      <c r="I30">
         <v>5</v>
       </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
       <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
         <v>400</v>
       </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C31" t="s">
@@ -2453,23 +1952,26 @@
         <v>18</v>
       </c>
       <c r="H31">
+        <v>0.15</v>
+      </c>
+      <c r="I31">
         <v>3</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>2</v>
       </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
       <c r="K31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" t="s">
         <v>73</v>
       </c>
       <c r="C32" t="s">
@@ -2488,23 +1990,26 @@
         <v>6</v>
       </c>
       <c r="H32">
+        <v>0.1</v>
+      </c>
+      <c r="I32">
         <v>2</v>
       </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" t="s">
         <v>74</v>
       </c>
       <c r="C33" t="s">
@@ -2523,23 +2028,26 @@
         <v>12</v>
       </c>
       <c r="H33">
+        <v>0.25</v>
+      </c>
+      <c r="I33">
         <v>3</v>
       </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
       <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
         <v>221</v>
       </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="L33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" t="s">
         <v>76</v>
       </c>
       <c r="C34" t="s">
@@ -2558,23 +2066,26 @@
         <v>1</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
         <v>331</v>
       </c>
-      <c r="K34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="L34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" t="s">
         <v>79</v>
       </c>
       <c r="C35" t="s">
@@ -2593,23 +2104,26 @@
         <v>30</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
         <v>366</v>
       </c>
-      <c r="K35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="L35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" t="s">
         <v>81</v>
       </c>
       <c r="C36" t="s">
@@ -2619,7 +2133,7 @@
         <v>82</v>
       </c>
       <c r="E36">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="F36">
         <v>60</v>
@@ -2628,23 +2142,26 @@
         <v>8</v>
       </c>
       <c r="H36">
+        <v>0.1</v>
+      </c>
+      <c r="I36">
         <v>2</v>
       </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
       <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
         <v>309</v>
       </c>
-      <c r="K36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="L36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" t="s">
         <v>83</v>
       </c>
       <c r="C37" t="s">
@@ -2663,23 +2180,26 @@
         <v>12</v>
       </c>
       <c r="H37">
+        <v>0.25</v>
+      </c>
+      <c r="I37">
         <v>3</v>
       </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
       <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
         <v>240</v>
       </c>
-      <c r="K37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="L37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" t="s">
         <v>85</v>
       </c>
       <c r="C38" t="s">
@@ -2698,19 +2218,22 @@
         <v>16</v>
       </c>
       <c r="H38">
+        <v>0.25</v>
+      </c>
+      <c r="I38">
         <v>4</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
       <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
         <v>256</v>
       </c>
-      <c r="K38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="L38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2733,36 +2256,38 @@
         <v>40</v>
       </c>
       <c r="H39">
+        <v>0.15</v>
+      </c>
+      <c r="I39">
         <v>4</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
       <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
         <v>215</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="62" style="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>89</v>
       </c>
@@ -2770,7 +2295,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>91</v>
       </c>
@@ -2778,7 +2303,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>92</v>
       </c>
@@ -2786,7 +2311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>93</v>
       </c>
@@ -2794,31 +2319,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>94</v>
       </c>
       <c r="B5">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
         <v>95</v>
       </c>
       <c r="B6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>96</v>
       </c>
       <c r="B7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
         <v>97</v>
       </c>
@@ -2826,120 +2351,119 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
         <v>98</v>
       </c>
       <c r="B9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A10" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A11" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B10">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="3" t="s">
+      <c r="B12">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B11">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="3" t="s">
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="27" x14ac:dyDescent="0.15">
+      <c r="A14" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B12">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="3" t="s">
+      <c r="B14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="27" spans="1:2">
-      <c r="A14" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="B15" s="1">
         <v>10</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="12" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" t="s">
         <v>105</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>106</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>107</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>108</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>109</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>110</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>111</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>112</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>113</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>114</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>115</v>
       </c>
-      <c r="L1" t="s">
-        <v>116</v>
-      </c>
-      <c r="M1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2954,10 +2478,10 @@
         <v>60</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>30</v>
@@ -2972,16 +2496,16 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L2">
         <v>180</v>
       </c>
       <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2996,10 +2520,10 @@
         <v>72</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G3">
         <v>32</v>
@@ -3008,22 +2532,22 @@
         <v>37</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L3">
         <v>180</v>
       </c>
       <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3038,7 +2562,7 @@
         <v>84</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>1.4</v>
@@ -3050,22 +2574,22 @@
         <v>43</v>
       </c>
       <c r="I4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J4">
-        <v>1.05392156862745</v>
+        <v>1.0539215686274499</v>
       </c>
       <c r="K4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L4">
         <v>180</v>
       </c>
       <c r="M4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3080,10 +2604,10 @@
         <v>96</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="G5">
         <v>36</v>
@@ -3092,22 +2616,22 @@
         <v>57</v>
       </c>
       <c r="I5">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J5">
         <v>1.31944444444444</v>
       </c>
       <c r="K5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L5">
         <v>180</v>
       </c>
       <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3122,10 +2646,10 @@
         <v>108</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G6">
         <v>38</v>
@@ -3137,19 +2661,19 @@
         <v>50</v>
       </c>
       <c r="J6">
-        <v>1.55701754385965</v>
+        <v>1.5570175438596501</v>
       </c>
       <c r="K6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L6">
         <v>180</v>
       </c>
       <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3164,10 +2688,10 @@
         <v>120</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="G7">
         <v>40</v>
@@ -3182,16 +2706,16 @@
         <v>1.75</v>
       </c>
       <c r="K7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L7">
         <v>180</v>
       </c>
       <c r="M7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3206,10 +2730,10 @@
         <v>132</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G8">
         <v>42</v>
@@ -3224,16 +2748,16 @@
         <v>1.9047619047619</v>
       </c>
       <c r="K8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L8">
         <v>180</v>
       </c>
       <c r="M8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3248,10 +2772,10 @@
         <v>144</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="G9">
         <v>44</v>
@@ -3263,19 +2787,19 @@
         <v>80</v>
       </c>
       <c r="J9">
-        <v>2.04545454545455</v>
+        <v>2.0454545454545499</v>
       </c>
       <c r="K9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L9">
         <v>180</v>
       </c>
       <c r="M9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3290,10 +2814,10 @@
         <v>156</v>
       </c>
       <c r="E10">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>46</v>
@@ -3305,19 +2829,19 @@
         <v>90</v>
       </c>
       <c r="J10">
-        <v>2.17391304347826</v>
+        <v>2.1739130434782599</v>
       </c>
       <c r="K10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L10">
         <v>180</v>
       </c>
       <c r="M10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3332,10 +2856,10 @@
         <v>168</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F11">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="G11">
         <v>48</v>
@@ -3347,84 +2871,83 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>2.29166666666667</v>
+        <v>2.2916666666666701</v>
       </c>
       <c r="K11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L11">
         <v>180</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="18.725" customWidth="1"/>
+    <col min="1" max="1" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B1">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B2">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>